--- a/results/job_matches_2026-09-02.xlsx
+++ b/results/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G97"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>WIS International</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.8</v>
+        <v>21.5</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,49 +496,49 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
+          <t>https://www.indeed.com/viewjob?jk=7e1b49079cb03df4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Dallas</t>
+          <t>AI Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>18.8</v>
+        <v>20.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bc87d8d4b72fa4</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
+          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
+          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Dallas</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
+          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pharma Data Engineer – Databricks AWS</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c01255fde37758</t>
+          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Backend Go Developer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Datasage Technologies</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37c3bd53b7199c8</t>
+          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Pharma Data Engineer – Databricks AWS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d72577f6e997de</t>
+          <t>https://www.indeed.com/viewjob?jk=79c01255fde37758</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Engineer, Data and Insights</t>
+          <t>Backend Go Developer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>United Jewish Appeal-Fed of Jewish</t>
+          <t>Datasage Technologies</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
+          <t>https://www.indeed.com/viewjob?jk=e37c3bd53b7199c8</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127ac581bc7c947</t>
+          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Security Data Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Neumo Holdings LLC</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
+          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer, Data and Insights</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
+          <t>United Jewish Appeal-Fed of Jewish</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72936d7adf83912</t>
+          <t>https://www.indeed.com/viewjob?jk=9127ac581bc7c947</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Senior Security Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
+          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=f72936d7adf83912</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
+          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,164 +1161,164 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Full-Time Analyst - 2027 Data Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f92c9f4c62df8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
+          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Steelcase</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,14 +1336,14 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
+          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Campus Undergraduate Full-Time Analyst - 2027 Data Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1371,14 +1371,14 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
+          <t>https://www.indeed.com/viewjob?jk=9f92c9f4c62df8b2</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c077d0d8d52c113</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forward deployed engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3c077d0d8d52c113</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
+          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0ef720fc915d5a7</t>
+          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, PostgreSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b089978304c281b</t>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
+          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Consulting SWE</t>
+          <t>Forward deployed engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer + HPC</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
+          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
+          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
         </is>
       </c>
     </row>
@@ -2013,20 +2013,20 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c3f1635bd7570e</t>
+          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4d347d17e2c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>13.9</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Agero</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (B2B Scores)</t>
+          <t>Consulting SWE</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
+          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer + HPC</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,67 +2246,67 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer - CHG (Hybrid)</t>
+          <t>Data Engineer (Knowledge Graph)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Technical Architect - I_Azure DataBricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,67 +2316,67 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Epic Ambulatory Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c3f1635bd7570e</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>E-INFOSOL LLC</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,19 +2491,19 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
+          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2512,11 +2512,11 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,32 +2526,32 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,32 +2561,32 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,67 +2596,67 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Advisor II, Data Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
+          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
+          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be26e9957dff2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Principle SRE</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Merative</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>SiloSmashers</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
+          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
+          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Software Dev/Data Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GROWMARK</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Architecture - Sr Advisor I</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Fiserv</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56e2bc0bf1616b18</t>
+          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Browser Extension Platform</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer, Identity and Access Management</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Fitch Group</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>12.5</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, API Gateway, IAM, Oracle, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4316a6d89bd9dfac</t>
+          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA053</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA051</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,102 +3051,102 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
+          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,32 +3191,32 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,32 +3226,32 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Agentic Data Engineer (IC3)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
+          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
+          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,102 +3366,102 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Ecentria</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406a68ec242bd018</t>
+          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,32 +3506,32 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
+          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,32 +3541,32 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642d9d492b002566</t>
+          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156dda493f603ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b313a1b84f660028</t>
+          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cb1cfad2ce1fa38</t>
+          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Java Developer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5af3bc833528c5f0</t>
+          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Python Solutions Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD, Python</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e9dce9e97399ebe</t>
+          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI/AL Architect</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Flash Inspector</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,77 +3751,2247 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Specialist IS Business Systems Analyst</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>10.4</v>
+        <v>12.5</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Louisville, KY, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>New Orleans, LA, US USA</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Indianapolis, IN, US USA</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Hartford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Colorado Springs, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Stamford, CT, US USA</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Jacksonville, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Denver, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Gilbert, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Costa Mesa, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Deloitte</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Big Data Engineer</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Agero</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Medford, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>Sr Software Engineer (B2B Scores)</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>FICO</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>GRP Solutions</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Dayton, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>DevOps / AgentOps Engineer</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Kennesaw, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Technical Architect - I_Azure DataBricks</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>VeeRteq Solutions Inc.</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Epic Ambulatory Analyst</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Vnsure Business Solution</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Senior SecDevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Re:Build Manufacturing</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Senior SecDevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Re:Build Manufacturing</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Senior SecDevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Re:Build Manufacturing</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>SWE &amp; App Arch Engineer</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>PepsiCo</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Senior Cloud Engineer</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Fandom</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>DocuSign</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>THEMESOFT</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Sunnyvale, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>SAP ABAP Developer</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Ford Motor Company</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Livonia, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b25acd1aa7c0e4f9</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>MACH INDUSTRIES</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Los Angeles, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bab280546ddf807d</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Salesforce Development Engineer II</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>GM Financial</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Arlington, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Test Automation Engineer</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8be26e9957dff2b5</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Principle SRE</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Merative</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Data Architect</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SiloSmashers</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Senior Application Developer</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>VIVA</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f93002e908ca634d</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Software Dev/Data Engineer</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>GROWMARK</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>Sr Data Engineering Architect – Fraud Domain</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Realign</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Cleveland, OH, US USA</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Senior Software Architect, Browser Extension Platform</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Keeper Security, Inc.</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>AI &amp; Data Scientist Intern</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Ingredion</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Westchester, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - PA053</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - PA051</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>ZoomInfo</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Bethesda, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>State Farm</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Bloomington, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Child Mind Institute</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>OpenShift Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Senior Platform &amp; SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>Viventium Software</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Senior Agentic Data Engineer (IC3)</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>ClassLink, Inc.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Bellevue, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Data Engineer - Sr. Consultant level</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Visa</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Senior Platform &amp; SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G148" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Cloud Solution Engineer</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Zomedica Inc.</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Roswell, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>AWS, Lambda, Kinesis, S3, Azure, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16373240a782711f</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Kafka Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=406a68ec242bd018</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Full Stack Solutions Developer – Java</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G151" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Senior AI Engineer (Agent OS Platform)</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>ServiceTitan</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=642d9d492b002566</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=156dda493f603ad2</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Seattle, WA, US USA</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a194a6d7b2f441c1</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>GEICO</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Palo Alto, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4f114e4e73e60ddb</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI/AL Architect</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Flash Inspector</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Truist</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Devops Engineer</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
           <t>Prodapt Solutions</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Portland, OR, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
         <v>10.4</v>
       </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Database Administrator (Remote)</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Neumo Holdings LLC</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e97f3541b9b4ed92</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-02.xlsx
+++ b/results/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:G157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1378,17 +1378,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
+          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Backend Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Fellow</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, Scala, PostgreSQL, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c077d0d8d52c113</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,24 +1721,24 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
+          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
+          <t>Forward deployed engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>US Foods</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Production Support Engineering PMTS</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
+          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Forward deployed engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
+          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
+          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist, Technology Engineer (AWS)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Consulting SWE</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>DevOps Engineer + HPC</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer (Knowledge Graph)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,32 +2176,32 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Consulting SWE</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,32 +2211,32 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DevOps Engineer + HPC</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer (Knowledge Graph)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c3f1635bd7570e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>E-INFOSOL LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
+          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c3f1635bd7570e</t>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>E-INFOSOL LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
+          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
+          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
+          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
+          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
+          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
+          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
+          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
+          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
+          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
+          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
+          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
+          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
+          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
+          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
+          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
+          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
+          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
+          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
+          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
+          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,7 +4031,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
         </is>
       </c>
     </row>
@@ -4083,7 +4083,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4101,7 +4101,7 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
+          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
         </is>
       </c>
     </row>
@@ -4118,7 +4118,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,7 +4206,7 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
+          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4223,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4241,32 +4241,32 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
+          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Agero</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Sr Software Engineer (B2B Scores)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
+          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Software Engineer Senior - Mortgage Platforms</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Agero</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
+          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (B2B Scores)</t>
+          <t>Tech Consultant - SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Technical Architect - I_Azure DataBricks</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
+          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Technical Architect - I_Azure DataBricks</t>
+          <t>Infrastructure Engineer-Intermediate Level</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,7 +4521,7 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
         </is>
       </c>
     </row>
@@ -4983,17 +4983,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Dev/Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>SiloSmashers</t>
+          <t>GROWMARK</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,19 +5011,19 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>VIVA</t>
+          <t>SiloSmashers</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Scala, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f93002e908ca634d</t>
+          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Dev/Data Engineer</t>
+          <t>Sr Data Engineering Architect – Fraud Domain</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GROWMARK</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain</t>
+          <t>Senior Software Architect, Browser Extension Platform</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Browser Extension Platform</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Senior Software Engineer - PA053</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA053</t>
+          <t>Senior Software Engineer - PA051</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5221,24 +5221,24 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA051</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,29 +5281,29 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Senior Agentic Data Engineer (IC3)</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Agentic Data Engineer (IC3)</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
+          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,34 +5526,34 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
+          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Senior Technical Support Engineer</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, MySQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+          <t>https://www.indeed.com/viewjob?jk=61ca618a0f0d4d0d</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+          <t>Senior Engineer – CircleCard Platform</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,17 +5596,17 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf78b0dea5c3485</t>
         </is>
       </c>
     </row>
@@ -5718,17 +5718,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior AI Engineer (Agent OS Platform)</t>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Snowflake, SQL Server, PostgreSQL, Maven, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=642d9d492b002566</t>
+          <t>https://www.indeed.com/viewjob?jk=156dda493f603ad2</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular</t>
+          <t>Cloud &amp; AI/AL Architect</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Flash Inspector</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=156dda493f603ad2</t>
+          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
         </is>
       </c>
     </row>
@@ -5858,17 +5858,17 @@
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI/AL Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Flash Inspector</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,77 +5921,7 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Prodapt Solutions</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Database Administrator (Remote)</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Neumo Holdings LLC</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>TX, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e97f3541b9b4ed92</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-02.xlsx
+++ b/results/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G151"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,7 +538,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
+          <t>Managing Consultant, Databricks Engineer - Richmond</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,14 +566,14 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
+          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Dallas</t>
+          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -583,7 +583,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -601,14 +601,14 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
+          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
+          <t>Managing Consultant, Databricks Engineer - Dallas</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,7 +706,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
+          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
         </is>
       </c>
     </row>
@@ -748,52 +748,52 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Backend Go Developer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Datasage Technologies</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37c3bd53b7199c8</t>
+          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Neumo Holdings LLC</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
+          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Data Engineer, Data and Insights</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Neumo Holdings LLC</t>
+          <t>United Jewish Appeal-Fed of Jewish</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
+          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Engineer, Data and Insights</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>United Jewish Appeal-Fed of Jewish</t>
+          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
+          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127ac581bc7c947</t>
+          <t>https://www.indeed.com/viewjob?jk=f72936d7adf83912</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Security Data Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
+          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,34 +1011,34 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72936d7adf83912</t>
+          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,17 +1081,17 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,129 +1196,129 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Steelcase</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Campus Undergraduate Full-Time Analyst - 2027 Data Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=9f92c9f4c62df8b2</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
+          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Steelcase</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Full-Time Analyst - 2027 Data Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,67 +1371,67 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f92c9f4c62df8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
+          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
+          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>US Foods</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,34 +1606,34 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,42 +1641,42 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
+          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
+          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Forward deployed engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
+          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Production Support Engineering PMTS</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
+          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Production Support Engineering PMTS</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,67 +1896,67 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
+          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist, Technology Engineer (AWS)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>DevOps Engineer + HPC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Data Engineer (Knowledge Graph)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,67 +2001,67 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Consulting SWE</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>DevOps Engineer + HPC</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer (Knowledge Graph)</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>E-INFOSOL LLC</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
+          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,14 +2316,14 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
+          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
+          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Azure Cloud Architect</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Naperville, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8c3f1635bd7570e</t>
+          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>E-INFOSOL LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
+          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
+          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
+          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
+          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
+          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
+          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
+          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
+          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
+          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
+          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
+          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
+          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
+          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
+          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
+          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
+          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
+          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
+          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
+          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
+          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
+          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
+          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
+          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
+          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
+          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
         </is>
       </c>
     </row>
@@ -3978,7 +3978,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3996,7 +3996,7 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
+          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
         </is>
       </c>
     </row>
@@ -4013,7 +4013,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4031,67 +4031,67 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Application Developers | Data engineers</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Luxoft</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Cloud Storage, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdfeaad78ff66fdb</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Agero</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
+          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
+          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Sr Software Engineer (B2B Scores)</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Software Engineer Senior - Mortgage Platforms</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
+          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Tech Consultant - SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
+          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Agero</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (B2B Scores)</t>
+          <t>Technical Architect - I_Azure DataBricks</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Infrastructure Engineer-Intermediate Level</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Engineer Senior - Mortgage Platforms</t>
+          <t>Epic Ambulatory Analyst</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,32 +4381,32 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
+          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Tech Consultant - SDET / Test Automation Architect</t>
+          <t>SWE &amp; App Arch Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,32 +4416,32 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
+          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,32 +4451,32 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
+          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Technical Architect - I_Azure DataBricks</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
+          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
+          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer-Intermediate Level</t>
+          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Epic Ambulatory Analyst</t>
+          <t>SAP ABAP Developer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
+          <t>https://www.indeed.com/viewjob?jk=b25acd1aa7c0e4f9</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>MACH INDUSTRIES</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
+          <t>https://www.indeed.com/viewjob?jk=bab280546ddf807d</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
+          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
+          <t>https://www.indeed.com/viewjob?jk=8be26e9957dff2b5</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>SWE &amp; App Arch Engineer</t>
+          <t>Principle SRE</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Merative</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Dev/Data Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>GROWMARK</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
+          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>SiloSmashers</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
+          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer</t>
+          <t>Sr Data Engineering Architect – Fraud Domain</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25acd1aa7c0e4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior Software Architect, Browser Extension Platform</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>MACH INDUSTRIES</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,32 +4871,32 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab280546ddf807d</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,19 +4941,19 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be26e9957dff2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Principle SRE</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Merative</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4962,11 +4962,11 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Software Dev/Data Engineer</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>GROWMARK</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>SiloSmashers</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
+          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain</t>
+          <t>Senior Agentic Data Engineer (IC3)</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Browser Extension Platform</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA053</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA051</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Senior Software Engineer - PA053</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer - PA051</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Agentic Data Engineer (IC3)</t>
+          <t>Senior Databricks Data Engineer - Reliability</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,24 +5396,24 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
+          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Technical Support Engineer</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Flexera</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, MySQL, CI/CD, Kubernetes</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
+          <t>https://www.indeed.com/viewjob?jk=61ca618a0f0d4d0d</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Engineer – CircleCard Platform</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Target</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Brooklyn Park, MN, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -5466,24 +5466,24 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
+          <t>https://www.indeed.com/viewjob?jk=fbf78b0dea5c3485</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Cloud Solution Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Zomedica Inc.</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Lambda, Kinesis, S3, Azure, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5501,24 +5501,24 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+          <t>https://www.indeed.com/viewjob?jk=16373240a782711f</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5526,29 +5526,29 @@
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+          <t>https://www.indeed.com/viewjob?jk=406a68ec242bd018</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -5561,7 +5561,7 @@
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, MySQL, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
@@ -5571,24 +5571,24 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ca618a0f0d4d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Senior Engineer – CircleCard Platform</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5596,7 +5596,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -5606,24 +5606,24 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf78b0dea5c3485</t>
+          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Cloud Solution Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Zomedica Inc.</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Azure, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16373240a782711f</t>
+          <t>https://www.indeed.com/viewjob?jk=a194a6d7b2f441c1</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=406a68ec242bd018</t>
+          <t>https://www.indeed.com/viewjob?jk=4f114e4e73e60ddb</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5710,216 +5710,6 @@
         </is>
       </c>
       <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Cognizant</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Lake Mary, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=156dda493f603ad2</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Cloud &amp; AI/AL Architect</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Flash Inspector</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a194a6d7b2f441c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f114e4e73e60ddb</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Prodapt Solutions</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
         </is>

--- a/results/job_matches_2026-09-02.xlsx
+++ b/results/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G151"/>
+  <dimension ref="A1:G145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,87 +468,87 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Data Analytics Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WIS International</t>
+          <t>Molex</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Lisle, IL, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>20.1</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Event Hubs, GCP, Hadoop, Spark</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e1b49079cb03df4</t>
+          <t>https://www.indeed.com/viewjob?jk=c5bc87d8d4b72fa4</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Data Analytics Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Richmond</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Molex</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Lisle, IL, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>20.1</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Kafka, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5bc87d8d4b72fa4</t>
+          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Richmond</t>
+          <t>Data &amp; AI Architect – BD Excellence (BDE) Office</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>BD</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Franklin Lakes, NJ, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,112 +556,112 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=01e27baffa851f19</t>
+          <t>https://www.indeed.com/viewjob?jk=83656a632b29e691</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
+          <t>Senior Java Developer / Albany - NY / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
+          <t>https://www.indeed.com/viewjob?jk=55d5f237a320ef13</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Dallas</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
+          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>Neumo Holdings LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.8</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,67 +671,67 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
+          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>18.8</v>
+        <v>16</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Pharma Data Engineer – Databricks AWS</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>RadCube</t>
+          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>17.4</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,67 +741,67 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79c01255fde37758</t>
+          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
+          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Neumo Holdings LLC</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,59 +811,59 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
+          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Data Engineer, Data and Insights</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>United Jewish Appeal-Fed of Jewish</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
+          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f72936d7adf83912</t>
+          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,34 +941,34 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
+          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Liberty Mutual Insurance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Portsmouth, NH, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,17 +976,17 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
+          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,207 +1021,207 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Steelcase</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
+          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Globant</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
+          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Steelcase</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Full-Time Analyst - 2027 Data Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,94 +1266,94 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f92c9f4c62df8b2</t>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
+          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
+          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
+          <t>Production Support Engineering PMTS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>US Foods</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>The Iowa Clinic</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>West Des Moines, IA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,137 +1511,137 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,137 +1651,137 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
+          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
+          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Specialist, Technology Engineer (AWS)</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer (Knowledge Graph)</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,67 +1791,67 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Production Support Engineering PMTS</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
+          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,94 +1896,94 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>DevOps Engineer + HPC</t>
+          <t>Content Engineer II (E6175)</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>IEEE Corporate</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Piscataway, NJ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Lambda, S3, RDS, Scala, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
+          <t>https://www.indeed.com/viewjob?jk=2af3f922995d21c0</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer (Knowledge Graph)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,34 +1991,34 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>E-INFOSOL LLC</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,14 +2141,14 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
+          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
+          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>E-INFOSOL LLC</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Morristown, NJ, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
+          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
+          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
+          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Rosslyn, VA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
+          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
+          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
+          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
+          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
+          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
+          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
+          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
+          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
         </is>
       </c>
     </row>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
         </is>
       </c>
     </row>
@@ -2788,7 +2788,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Mechanicsburg, PA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
         </is>
       </c>
     </row>
@@ -2823,7 +2823,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
+          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
+          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2911,7 +2911,7 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
+          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
         </is>
       </c>
     </row>
@@ -2928,7 +2928,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2981,7 +2981,7 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
+          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2998,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
+          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Princeton, NJ, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3051,7 +3051,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
+          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
         </is>
       </c>
     </row>
@@ -3068,7 +3068,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
+          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3121,7 +3121,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
+          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
         </is>
       </c>
     </row>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3156,7 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
+          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
         </is>
       </c>
     </row>
@@ -3173,7 +3173,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
         </is>
       </c>
     </row>
@@ -3208,7 +3208,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3226,7 +3226,7 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
         </is>
       </c>
     </row>
@@ -3243,7 +3243,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
+          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Davenport, IA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
+          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
+          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jericho, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
         </is>
       </c>
     </row>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Louisville, KY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3401,7 +3401,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
+          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
         </is>
       </c>
     </row>
@@ -3418,7 +3418,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>New Orleans, LA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,7 +3471,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
+          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
         </is>
       </c>
     </row>
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
+          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3523,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Hartford, CT, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,7 +3576,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
+          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
         </is>
       </c>
     </row>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3611,7 +3611,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
         </is>
       </c>
     </row>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Colorado Springs, CO, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3646,7 +3646,7 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3663,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Stamford, CT, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
+          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
         </is>
       </c>
     </row>
@@ -3698,7 +3698,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
         </is>
       </c>
     </row>
@@ -3733,7 +3733,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Colorado Springs, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3751,7 +3751,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
+          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
         </is>
       </c>
     </row>
@@ -3768,7 +3768,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Stamford, CT, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3786,7 +3786,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
+          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
         </is>
       </c>
     </row>
@@ -3803,7 +3803,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
+          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
         </is>
       </c>
     </row>
@@ -3838,7 +3838,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Gilbert, AZ, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3856,7 +3856,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
+          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
         </is>
       </c>
     </row>
@@ -3873,7 +3873,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Costa Mesa, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
+          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
         </is>
       </c>
     </row>
@@ -3908,7 +3908,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
+          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Agero</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Gilbert, AZ, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
+          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Sr Software Engineer (B2B Scores)</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Costa Mesa, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
+          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Application Developers | Data engineers</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Luxoft</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Cloud Storage, Spark, PySpark, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdfeaad78ff66fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bc14828ef1e67f</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Agero</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
+          <t>https://www.indeed.com/viewjob?jk=1988c96da6897747</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>GRP Solutions</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bf817aa82ff453</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr Software Engineer (B2B Scores)</t>
+          <t>Tech Consultant - SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,7 +4161,7 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,7 +4171,7 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
+          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
         </is>
       </c>
     </row>
@@ -4213,17 +4213,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Tech Consultant - SDET / Test Automation Architect</t>
+          <t>Infrastructure Engineer-Intermediate Level</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,7 +4241,7 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
+          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
         </is>
       </c>
     </row>
@@ -4283,17 +4283,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Technical Architect - I_Azure DataBricks</t>
+          <t>Epic Ambulatory Analyst</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Delta Live Tables, Scala, Databricks Lakehouse, SQL Server, ELT</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0074d6a4018f22e0</t>
+          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer-Intermediate Level</t>
+          <t>Senior Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>SCOR</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Epic Ambulatory Analyst</t>
+          <t>SWE &amp; App Arch Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Vnsure Business Solution</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
+          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
+          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>SWE &amp; App Arch Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,24 +4416,24 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
+          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>DocuSign</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
+          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
+          <t>Software Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>THEMESOFT</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
+          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>SAP ABAP Developer</t>
+          <t>Senior Technical Architect Information Technology</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Ford Motor Company</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Livonia, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Hadoop, MapReduce, Spark, Scala, Oracle, SQL Server, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,24 +4556,24 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b25acd1aa7c0e4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=50aa46a4f9956022</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>SAP ABAP Developer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>MACH INDUSTRIES</t>
+          <t>Ford Motor Company</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Livonia, MI, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bab280546ddf807d</t>
+          <t>https://www.indeed.com/viewjob?jk=b25acd1aa7c0e4f9</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>MACH INDUSTRIES</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,19 +4626,19 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
+          <t>https://www.indeed.com/viewjob?jk=bab280546ddf807d</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Principle SRE</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Merative</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8be26e9957dff2b5</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Principle SRE</t>
+          <t>Software Dev/Data Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Merative</t>
+          <t>GROWMARK</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Dev/Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>GROWMARK</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,7 +4766,7 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
+          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
         </is>
       </c>
     </row>
@@ -4808,25 +4808,25 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,32 +4836,32 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Browser Extension Platform</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Storage Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,34 +4896,34 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,19 +5046,19 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Agentic Data Engineer (IC3)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>ClassLink, Inc.</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
+          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Data Engineer - Sr. Consultant level</t>
+          <t>Senior Agentic Data Engineer (IC3)</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
+          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,24 +5186,24 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+          <t>Sr. Database Developer</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Herschend Family Entertainment</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,34 +5211,34 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>Cloud Solution Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Zomedica Inc.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Roswell, GA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, Lambda, Kinesis, S3, Azure, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,24 +5256,24 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
+          <t>https://www.indeed.com/viewjob?jk=16373240a782711f</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=a194a6d7b2f441c1</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA053</t>
+          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,7 +5316,7 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -5326,24 +5326,24 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+          <t>https://www.indeed.com/viewjob?jk=4f114e4e73e60ddb</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA051</t>
+          <t>Senior Databricks Data Engineer - Reliability</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5351,7 +5351,7 @@
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
@@ -5361,24 +5361,24 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer - Reliability</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -5396,19 +5396,19 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Senior Technical Support Engineer</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Flexera</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -5421,7 +5421,7 @@
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Azure, Google Cloud Platform, GCP, Scala, MySQL, CI/CD, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
@@ -5431,24 +5431,24 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61ca618a0f0d4d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Senior Engineer – CircleCard Platform</t>
+          <t>Software Engineer Full stack</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Target</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Brooklyn Park, MN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5456,34 +5456,34 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbf78b0dea5c3485</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Cloud Solution Engineer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Zomedica Inc.</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Roswell, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, Azure, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -5500,216 +5500,6 @@
         </is>
       </c>
       <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16373240a782711f</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Kafka Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Event Hubs, Spark, Kafka, Kafka Connect, Terraform, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=406a68ec242bd018</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a194a6d7b2f441c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f114e4e73e60ddb</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Prodapt Solutions</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
         </is>

--- a/results/job_matches_2026-09-02.xlsx
+++ b/results/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G145"/>
+  <dimension ref="A1:G91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -573,17 +573,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Java Developer / Albany - NY / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Enterprise Applications Developer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Beta Bionics, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,42 +591,42 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, SQS, SNS, API Gateway, ECS</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55d5f237a320ef13</t>
+          <t>https://www.indeed.com/viewjob?jk=55a36044a8c65468</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Senior Java Developer / Albany - NY / Onsite 3 - 4 Days a Week</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Strategic Mindz LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>Albany, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
+          <t>https://www.indeed.com/viewjob?jk=55d5f237a320ef13</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Neumo Holdings LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
+          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
+          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
+          <t>Neumo Holdings LLC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,59 +741,59 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>AI/ML Data Scientist (GPSSC)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Warren, MI, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
+          <t>https://www.indeed.com/viewjob?jk=060ac516e5d04bc2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Data Engineer Technology</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Eli Lilly</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3921b775f4bfb3a3</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Providence, RI, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e7b5584b1a87e4b</t>
+          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,147 +906,147 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d3d0ed205376fb17</t>
+          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Steelcase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b8d05282c79331ea</t>
+          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Portsmouth, NH, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a129774c3b6c3e8d</t>
+          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Liberty Mutual Insurance</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>16</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, S3, SQS, API Gateway, ECS, RDS, Azure</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ee890dc40655c32</t>
+          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Steelcase</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,77 +1056,77 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Confiz</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
         </is>
       </c>
     </row>
@@ -1138,12 +1138,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Globant</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, IAM, Azure, Databricks, GCP, Impala, Spark, PySpark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=de3d10e4076147b8</t>
+          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,34 +1221,34 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
+          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
+          <t>Artificial Intelligence / Machine Learning Developer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>US Foods</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,77 +1256,77 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Production Support Engineering PMTS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-05-06</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
+          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,129 +1336,129 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
+          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Oracle, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2809f0da9bc6a08f</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Production Support Engineering PMTS</t>
+          <t>IT Specialist/Systems Administrator</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>The Manor</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Morrisville, VT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,217 +1466,217 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
+          <t>https://www.indeed.com/viewjob?jk=053e2f866a950d1f</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
+          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Specialist, Technology Engineer (AWS)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Software Engineer - Analytics</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Columbus, IN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,94 +1686,94 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer (Knowledge Graph)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer (Knowledge Graph)</t>
+          <t>Databricks Administration Specialist</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Buyers Edge Platform</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Content Engineer II (E6175)</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>IEEE Corporate</t>
+          <t>E-INFOSOL LLC</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Piscataway, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,42 +1956,42 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, MySQL, NoSQL, CI/CD, Jenkins, Maven</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2af3f922995d21c0</t>
+          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,102 +2001,102 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=c29367938bda715b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
+          <t>https://www.indeed.com/viewjob?jk=8880f249d806c24c</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
+          <t>https://www.indeed.com/viewjob?jk=aa66504dec0a5f5c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
+          <t>Big Data Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>Agero</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Medford, MA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,277 +2106,277 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>E-INFOSOL LLC</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa2c8c48e2498cf</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=778d1b72e0567b95</t>
+          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48fb65dd35fe2307</t>
+          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Morristown, NJ, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=496e1c6c66926d88</t>
+          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4deae01c6a6686c9</t>
+          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=562b07a165d95ed9</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Architect - Python 8+ Years</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Velosys</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Rosslyn, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=394f624103f3ac06</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b96c8f95f45de8</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21794eae441b6843</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bf817aa82ff453</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Tech Consultant - SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=628ab10542a9a42e</t>
+          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Software Engineer Senior - Mortgage Platforms</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e67eaa88eba9af1d</t>
+          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Infrastructure Engineer-Intermediate Level</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=047917358e7012db</t>
+          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,172 +2526,172 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e0e9af2383ade0da</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Redwood City, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb92712556bdf9a3</t>
+          <t>https://www.indeed.com/viewjob?jk=d9bc14828ef1e67f</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Attain</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5dd23814a5363ac</t>
+          <t>https://www.indeed.com/viewjob?jk=1988c96da6897747</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3c1d09517048c4c4</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>SCOR</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a0f563a8ea34f62</t>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>SWE &amp; App Arch Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a26de6fcc547eda</t>
+          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,102 +2736,102 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=66eb0c1dd6801423</t>
+          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Software Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f51340d14d8a49dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Mechanicsburg, PA, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba68ab0255d7215</t>
+          <t>https://www.indeed.com/viewjob?jk=b38b2d7dd112b433</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Technical Architect Information Technology</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>NewYork-Presbyterian Hospital</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Hadoop, MapReduce, Spark, Scala, Oracle, SQL Server, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3f5b7dfa01746cb7</t>
+          <t>https://www.indeed.com/viewjob?jk=50aa46a4f9956022</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a87ee22f7bf1a78</t>
+          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Salesforce Development Engineer II</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Dayton, OH, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,67 +2911,67 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81424bcfb0a4ec64</t>
+          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88ddb62688ddbea0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=743a058ece0dba52</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=901c71e6187e6a70</t>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>OpenShift Platform Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Princeton, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db83f93bfba180ac</t>
+          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e525cc270dd07a4b</t>
+          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Viventium Software</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,32 +3121,32 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a83be875dfd67bc3</t>
+          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,32 +3156,32 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c3321d42df031a71</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,207 +3191,207 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62d4974a15c6336c</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=509f76b9081eeae1</t>
+          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Entitlement I - Sr. Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08233903ec02c8ec</t>
+          <t>https://www.indeed.com/viewjob?jk=45974b9c03dac7e0</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>bluematrix</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Davenport, IA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Lambda, Kinesis, SQS, ECS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=427b0ee2a0c773dc</t>
+          <t>https://www.indeed.com/viewjob?jk=6eff3f3607854e4a</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2e1f531c14684ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Digital Platform Architect</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Comtek Intl</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Jericho, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Scala, Snowflake, NoSQL, Data Modeling, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3df6949a8a4197af</t>
+          <t>https://www.indeed.com/viewjob?jk=78e5b707656920a5</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Senior Databricks Data Engineer - Reliability</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Louisville, KY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=48c22010c93dd289</t>
+          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc00629b11c0163e</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New Orleans, LA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,32 +3471,32 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1500c3e228fd2624</t>
+          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Full Stack Solutions Developer – Java</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,2002 +3506,112 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08c22a98761ec7e1</t>
+          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Software Engineer Full stack</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d9bf7c11a00a5a1</t>
+          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>Sr. Database Developer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Herschend Family Entertainment</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1306ded654ee95ce</t>
+          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
+          <t>APPLICATION DEVELOPER</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>Atos</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Aurora, IL, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9a70b3bc7e63d3</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Colorado Springs, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=26d3e77c23e2db06</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Stamford, CT, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88492821d7f7ce72</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Jacksonville, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a088fbb56699a9ff</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6dc83c8db1a4ce3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf80c0041e58589f</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f5cced3942942c97</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Gilbert, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b1a53e7ff09b1e2f</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Costa Mesa, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0260c355d0366cec</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Cyber Identity - FDE Senior Consultant - Engineering and Product Engineer III</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Deloitte</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, S3, Azure, GCP, Vertex AI, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=383b03bef760ffc6</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Big Data Engineer</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Agero</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Medford, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Sr Software Engineer (B2B Scores)</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>FICO</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>GRP Solutions</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Dayton, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Attain</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Redwood City, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d9bc14828ef1e67f</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Attain</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>RDS, GCP, BigQuery, Spark, Scala, Dask, MLOps, CI/CD, Terraform, Docker</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1988c96da6897747</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>SDET / Test Automation Architect</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bf817aa82ff453</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Tech Consultant - SDET / Test Automation Architect</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>NTT DATA</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Software Engineer Senior - Mortgage Platforms</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer-Intermediate Level</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>USAA</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>San Antonio, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>DevOps / AgentOps Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Kennesaw, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Epic Ambulatory Analyst</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Vnsure Business Solution</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>11.8</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>SCOR</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>SWE &amp; App Arch Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>PepsiCo</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Senior Cloud Engineer</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Fandom</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>DocuSign</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>THEMESOFT</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Software Data Engineer/Data Scientist</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Senior Technical Architect Information Technology</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>NewYork-Presbyterian Hospital</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>RDS, Hadoop, MapReduce, Spark, Scala, Oracle, SQL Server, ETL, Tableau, Git</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50aa46a4f9956022</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>SAP ABAP Developer</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Ford Motor Company</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>Livonia, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b25acd1aa7c0e4f9</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>MACH INDUSTRIES</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, ECS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bab280546ddf807d</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Principle SRE</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>Merative</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Software Dev/Data Engineer</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>GROWMARK</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>AI Product Engineer</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>BDIPlus</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Salesforce Development Engineer II</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Data Architect</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>SiloSmashers</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Software Development Engineer 2</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Twilio</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>AI &amp; Data Scientist Intern</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Ingredion</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Westchester, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Burlington Stores</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Edgewater Park, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Storage Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Pacific Gas and Electric</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Oakland, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Child Mind Institute</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>OpenShift Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Viventium Software</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Senior Agentic Data Engineer (IC3)</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>ClassLink, Inc.</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Data Engineer - Sr. Consultant level</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Bellevue, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Data Engineer - Sr. Consultant level</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Visa</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Sr. Database Developer</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Herschend Family Entertainment</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Peachtree Corners, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-09-02</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Cloud Solution Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>Zomedica Inc.</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>Roswell, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, Kinesis, S3, Azure, CI/CD, Azure DevOps, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16373240a782711f</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a194a6d7b2f441c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - (C#/Microservices/Azure)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>GEICO</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Palo Alto, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4f114e4e73e60ddb</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Senior Databricks Data Engineer - Reliability</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Scientific Games</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Alpharetta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Truist</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Full Stack Solutions Developer – Java</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Software Engineer Full stack</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>MD, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Oracle, MySQL, MongoDB, NoSQL, Docker, Kubernetes, AKS</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2023-01-15</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0ac8ff170c136339</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Devops Engineer</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Prodapt Solutions</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Irving, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
+          <t>https://www.indeed.com/viewjob?jk=88b7d6cdbfaa32a7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-02.xlsx
+++ b/results/job_matches_2026-09-02.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G91"/>
+  <dimension ref="A1:G93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,25 +608,25 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Java Developer / Albany - NY / Onsite 3 - 4 Days a Week</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Strategic Mindz LLC</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Albany, NY, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, ECS, RDS, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,24 +636,24 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55d5f237a320ef13</t>
+          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Edwards Lifesciences</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Irvine, CA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
@@ -661,7 +661,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Data Factory, Databricks, Blob Storage</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Databricks, GCP, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fce36bd18ab198a</t>
+          <t>https://www.indeed.com/viewjob?jk=8bb849225e8b2c49</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Databricks Data Engineer</t>
+          <t>Full Stack Product Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>EXL Service</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Raritan, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
+          <t>AWS, S3, API Gateway, Azure, Databricks, Spark, Scala, Polars, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
+          <t>https://www.indeed.com/viewjob?jk=5923f003c14c9207</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer (Remote)</t>
+          <t>Databricks Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Neumo Holdings LLC</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Raritan, NJ, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,34 +731,34 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Azure, Data Factory, Databricks, Unity Catalog</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
+          <t>https://www.indeed.com/viewjob?jk=9111ea89841eec4c</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AI/ML Data Scientist (GPSSC)</t>
+          <t>Senior Data Engineer (Remote)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Neumo Holdings LLC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Warren, MI, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,34 +766,34 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Databricks, Google Cloud Platform, BigQuery, Dataflow, Hadoop, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=060ac516e5d04bc2</t>
+          <t>https://www.indeed.com/viewjob?jk=56051797fb6b2162</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Engineer Technology</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Neptune Technology Group</t>
+          <t>Zifo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Duluth, GA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,7 +801,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
+          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
+          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Data Engineer Technology</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Zifo</t>
+          <t>Neptune Technology Group</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Duluth, GA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Google Cloud Platform, GCP, HBase, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Kinesis, Redshift, Step Functions, S3, Spark, PySpark, Scala, Spark Streaming</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=caf9cc910f59adeb</t>
+          <t>https://www.indeed.com/viewjob?jk=c40ccf2501b1a3b2</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Blue Cross &amp; Blue Shield of Rhode Island</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Synapse Analytics, Data Lake Storage, Scala, Snowflake, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=df59126c5c6a3dd1</t>
+          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>CE Data Architect</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Steelcase</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Grand Rapids, MI, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc48c4326b062b24</t>
+          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Steelcase</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Grand Rapids, MI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,29 +941,29 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Google Cloud Platform, GCP</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d35e48617ce425b3</t>
+          <t>https://www.indeed.com/viewjob?jk=a88f801e13f23bd8</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
+          <t>Data Integration Engineer II</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>mPulse Mobile</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Redshift, S3, Scala, Snowflake, SQL Server, PostgreSQL, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,59 +986,59 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
+          <t>https://www.indeed.com/viewjob?jk=3a99bb3c5f6b3d7d</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Digital Native Business)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
+          <t>https://www.indeed.com/viewjob?jk=b96553a6eed65411</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Dave</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,7 +1046,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, S3, RDS, Databricks, GCP, Hive, Spark, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1056,24 +1056,24 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
+          <t>https://www.indeed.com/viewjob?jk=287ed52d2d43bfba</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>US Foods</t>
+          <t>Dave</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Rosemont, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
+          <t>Redshift, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
+          <t>https://www.indeed.com/viewjob?jk=dc313996d778a984</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
+          <t>Intern – Data Engineer (Hybrid: Onsite &amp; Remote)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>US Foods</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Rosemont, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Spark, Kafka, Snowflake, Oracle, MySQL, ETL</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
+          <t>https://www.indeed.com/viewjob?jk=384534c24c687bf3</t>
         </is>
       </c>
     </row>
@@ -1168,17 +1168,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,34 +1186,34 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
+          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. AI/ML Engineer - Java Background - Remote</t>
+          <t>Specialist Solutions Architect - Data Engineering &amp; Warehousing (Financial Services)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, Splunk, CI/CD</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44d637a29cee0524</t>
+          <t>https://www.indeed.com/viewjob?jk=4e4215bed42cba68</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Artificial Intelligence / Machine Learning Developer</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Unissant</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ashburn, VA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,69 +1256,69 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
+          <t>https://www.indeed.com/viewjob?jk=776f5f1b56365c1e</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Production Support Engineering PMTS</t>
+          <t>Artificial Intelligence / Machine Learning Developer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>Unissant</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Ashburn, VA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Polars, PostgreSQL, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
+          <t>https://www.indeed.com/viewjob?jk=63de9516985bddfe</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>GCP Architect</t>
+          <t>Software Engineering Intern III, Summer 2027 (Onsite)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>J2B GLOBAL LLC</t>
+          <t>BAE Systems USA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, Azure, Kafka, Oracle, PostgreSQL, MySQL, MongoDB, DynamoDB, NoSQL, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
+          <t>https://www.indeed.com/viewjob?jk=02463d12db1e81b3</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Databricks Architect</t>
+          <t>Production Support Engineering PMTS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Sarasota, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
+          <t>AWS, S3, RDS, Spark, PySpark, Scala, PostgreSQL, MySQL, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
+          <t>https://www.indeed.com/viewjob?jk=6280b6bade74237a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Docuphase</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Saint Petersburg, FL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,17 +1396,17 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-03-20</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
+          <t>https://www.indeed.com/viewjob?jk=510b1e334c4fe4f9</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Saint Petersburg, FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
+          <t>https://www.indeed.com/viewjob?jk=d858dceda163f311</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>IT Specialist/Systems Administrator</t>
+          <t>DevOps Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>The Manor</t>
+          <t>Docuphase</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Morrisville, VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,69 +1466,69 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, CI/CD</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, CI/CD, Jenkins, Azure DevOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-03-20</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053e2f866a950d1f</t>
+          <t>https://www.indeed.com/viewjob?jk=c845115326a561bc</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Versant</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Orlando, FL, US USA</t>
+          <t>Sarasota, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
+          <t>https://www.indeed.com/viewjob?jk=9f7ff9e6a3329d1d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>E-solutions Inc</t>
+          <t>Vforce Infotech</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Malvern, PA, US USA</t>
+          <t>Edison, NJ, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
+          <t>https://www.indeed.com/viewjob?jk=39829992fff11c16</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Specialist, Technology Engineer (AWS)</t>
+          <t>Azure Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Nationwide Mutual Insurance Company</t>
+          <t>E-solutions Inc</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Malvern, PA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
+          <t>AWS, Azure, Cloud Storage, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
+          <t>https://www.indeed.com/viewjob?jk=eb0d6e400872c8fa</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Engineer - Analytics</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Schneider Electric</t>
+          <t>TripleLift</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Andover, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,42 +1606,42 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
+          <t>AWS, EMR, S3, RDS, Databricks, Spark, Kafka, Kafka Connect, Snowflake, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
+          <t>https://www.indeed.com/viewjob?jk=3e6ad14e926236dc</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>World Wide Technology</t>
+          <t>Versant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Orlando, FL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
+          <t>AWS, Glue, Lambda, Step Functions, RDS, Spark, Scala, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
+          <t>https://www.indeed.com/viewjob?jk=c083accf4ed493d3</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Overseas Contractor</t>
+          <t>Specialist, Technology Engineer (AWS)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Nationwide Mutual Insurance Company</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Quincy, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
+          <t>AWS, Lambda, Step Functions, S3, API Gateway, IAM, RDS, Azure, Scala, Splunk</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
+          <t>https://www.indeed.com/viewjob?jk=3ad18440ba3f8089</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer (Knowledge Graph)</t>
+          <t>Software Engineer - Analytics</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>VeeRteq Solutions Inc.</t>
+          <t>Schneider Electric</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Andover, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, Delta Live Tables, Spark, Scala, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,67 +1721,67 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
+          <t>https://www.indeed.com/viewjob?jk=6989e3e0e2abd957</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Python Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Pioneering Evolution</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Arlington, VA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Dataflow, Scala, NoSQL, Data Modeling, MLOps, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
+          <t>https://www.indeed.com/viewjob?jk=4285c04ca20cf636</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Databricks Administration Specialist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SBA Communications</t>
+          <t>Gravie</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Boca Raton, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, Unity Catalog, Spark, PySpark, Kafka, ELT</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,19 +1791,19 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
+          <t>https://www.indeed.com/viewjob?jk=a7b566070d802085</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>World Wide Technology</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Redshift, Databricks, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, Power BI, Tableau, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
+          <t>https://www.indeed.com/viewjob?jk=6c227e7fd18751f0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Solution Architect</t>
+          <t>Data Engineer (Knowledge Graph)</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Deloitte</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Hermitage, TN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Snowflake, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
+          <t>https://www.indeed.com/viewjob?jk=19609ee083f0bbaa</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Cloud Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Caterpillar</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Peoria, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Data Lake Storage, Blob Storage, Google Cloud Platform, Spark, Scala, Snowflake</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
+          <t>https://www.indeed.com/viewjob?jk=e4ef7032884f2d3a</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
+          <t>Overseas Contractor</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Nordstrom</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Quincy, MA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
+          <t>AWS, Glue, Lambda, S3, IAM, RDS, Databricks, Unity Catalog, Spark, PySpark</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
+          <t>https://www.indeed.com/viewjob?jk=2dec31a65ca0186f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Junior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>E-INFOSOL LLC</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
+          <t>https://www.indeed.com/viewjob?jk=cc20a22613db4d0e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c29367938bda715b</t>
+          <t>https://www.indeed.com/viewjob?jk=053d78d73ec03580</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Databricks Administration Specialist</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>SBA Communications</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Boca Raton, FL, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, ELT, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,67 +2036,67 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8880f249d806c24c</t>
+          <t>https://www.indeed.com/viewjob?jk=4208e11a4c185e66</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Solution Architect</t>
+          <t>Solution Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Deloitte</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Hermitage, TN, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Data Modeling, Dimensional Modeling, ETL, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Databricks, Event Hubs, Scala, Tableau, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aa66504dec0a5f5c</t>
+          <t>https://www.indeed.com/viewjob?jk=4a83fa56d22087cf</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Big Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Agero</t>
+          <t>Caterpillar</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Medford, MA, US USA</t>
+          <t>Peoria, IL, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Medallion Architecture, Scala, Snowflake, Oracle, Data Modeling, Dimensional Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Kinesis, S3, IAM, RDS, Azure, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,94 +2106,94 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38b142c6d7436546</t>
+          <t>https://www.indeed.com/viewjob?jk=bdc547e9d55801b0</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Software Engineer 2 (Hybrid - Seattle, WA)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Nordstrom</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7aa2c8c48e2498cf</t>
+          <t>https://www.indeed.com/viewjob?jk=e92eb5beb2f7a4a4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Junior DevOps Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>E-INFOSOL LLC</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
+          <t>https://www.indeed.com/viewjob?jk=53f488a664bfb365</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Spark, Scala, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
+          <t>https://www.indeed.com/viewjob?jk=7aa2c8c48e2498cf</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Data Engineer</t>
+          <t>Architect - Python 8+ Years</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Baker Tilly Canada</t>
+          <t>Velosys</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Milwaukee, WI, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
+          <t>AWS, Lambda, S3, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
+          <t>https://www.indeed.com/viewjob?jk=e6b96c8f95f45de8</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
+          <t>https://www.indeed.com/viewjob?jk=92972228a24c2ad3</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Madison, WI, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
+          <t>https://www.indeed.com/viewjob?jk=991c60d8a9d1e274</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Architect - Python 8+ Years</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Velosys</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Milwaukee, WI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6b96c8f95f45de8</t>
+          <t>https://www.indeed.com/viewjob?jk=130606ce4af82b2f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SDET / Test Automation Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e6bf817aa82ff453</t>
+          <t>https://www.indeed.com/viewjob?jk=3353189008ef9b63</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Tech Consultant - SDET / Test Automation Architect</t>
+          <t>Associate Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Baker Tilly Canada</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Madison, WI, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Scala, ETL, ELT, Power BI, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0976d9966b801b52</t>
+          <t>https://www.indeed.com/viewjob?jk=b3d754b9cf9c34e1</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer Senior - Mortgage Platforms</t>
+          <t>SDET / Test Automation Architect</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>USAA</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>RDS, Azure, Scala, Kafka, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,14 +2456,14 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
+          <t>https://www.indeed.com/viewjob?jk=e6bf817aa82ff453</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer-Intermediate Level</t>
+          <t>Software Engineer Senior - Mortgage Platforms</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Kafka, Snowflake, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
+          <t>https://www.indeed.com/viewjob?jk=00509eb9420ab687</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>DevOps / AgentOps Engineer</t>
+          <t>Infrastructure Engineer-Intermediate Level</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>USAA</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Kennesaw, GA, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
+          <t>AWS, Azure, Scala, Oracle, SQL Server, PostgreSQL, MySQL, Splunk, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
+          <t>https://www.indeed.com/viewjob?jk=2849394ab99f4a5f</t>
         </is>
       </c>
     </row>
@@ -2603,25 +2603,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Platform Engineer</t>
+          <t>Senior SDET - Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Northern Trust Corp.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,59 +2631,59 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
+          <t>https://www.indeed.com/viewjob?jk=a84bcd7ee72f8b17</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Data &amp; Analytics Engineer</t>
+          <t>DevOps / AgentOps Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>SCOR</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Kennesaw, GA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
+          <t>AWS, Lambda, Step Functions, S3, ECS, IAM, RDS, Azure, Vertex AI, CI/CD</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
+          <t>https://www.indeed.com/viewjob?jk=bf7a45b2edf278b0</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>SWE &amp; App Arch Engineer</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>PepsiCo</t>
+          <t>Octave</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
+          <t>AWS, Redshift, RDS, Medallion Architecture, GCP, BigQuery, Spark, Scala, Data Modeling, dbt</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
+          <t>https://www.indeed.com/viewjob?jk=c47d1c0284ef610c</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Platform Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Fandom</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,34 +2726,34 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Scala, Kafka, CI/CD, Terraform, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
+          <t>https://www.indeed.com/viewjob?jk=f0a56678723c20c5</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Data Engineer/Data Scientist</t>
+          <t>Senior Data &amp; Analytics Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>SCOR</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,34 +2761,34 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Snowflake, MySQL, Data Modeling, Snowflake Schema, Tableau</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2023-01-15</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
+          <t>https://www.indeed.com/viewjob?jk=f14465e046016fcb</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer</t>
+          <t>SWE &amp; App Arch Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Syngenta</t>
+          <t>PepsiCo</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, Databricks, Scala, Snowflake, PostgreSQL, dbt, Terraform, Docker, Kubernetes, Airflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b38b2d7dd112b433</t>
+          <t>https://www.indeed.com/viewjob?jk=29bc3b6bca49cc75</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Technical Architect Information Technology</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NewYork-Presbyterian Hospital</t>
+          <t>Fandom</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, MapReduce, Spark, Scala, Oracle, SQL Server, ETL, Tableau, Git</t>
+          <t>AWS, GCP, Scala, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=50aa46a4f9956022</t>
+          <t>https://www.indeed.com/viewjob?jk=3164f9cc4ca6cde8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>AI Product Engineer</t>
+          <t>Software Data Engineer/Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>BDIPlus</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>Azure, Hadoop, Hive, Spark, Scala, Kafka, Data Modeling, ETL, Tableau, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2023-01-15</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
+          <t>https://www.indeed.com/viewjob?jk=d866f8df02b8195b</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Salesforce Development Engineer II</t>
+          <t>Java Development Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,42 +2901,42 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Jenkins, Azure DevOps, Terraform</t>
+          <t>GCP, BigQuery, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, GitHub Actions, Maven</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=791008a46e54ae26</t>
+          <t>https://www.indeed.com/viewjob?jk=f9c4d5515734cd07</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Burlington Stores</t>
+          <t>Syngenta</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Edgewater Park, NJ, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
+          <t>AWS, Azure, GCP, Scala, ETL, ELT, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,54 +2946,54 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
+          <t>https://www.indeed.com/viewjob?jk=b38b2d7dd112b433</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Storage Platform Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>GXO Logistics</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, Snowflake, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
+          <t>https://www.indeed.com/viewjob?jk=6ab0ff5a1f596e09</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Product Engineer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Child Mind Institute</t>
+          <t>BDIPlus</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3002,11 +3002,11 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
+          <t>https://www.indeed.com/viewjob?jk=4537947394dff54d</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>OpenShift Platform Engineer</t>
+          <t>Cloud Data Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>TBC Corporation</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Palm Beach Gardens, FL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,34 +3041,34 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Oracle, SQL Server, PostgreSQL, DataOps, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=08ef9b7de75a6ddf</t>
+          <t>https://www.indeed.com/viewjob?jk=92ff61658113f0f6</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Software Development Engineer(Distributed Systems)</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Pleasanton, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, S3, ECS, RDS, Spark, Scala, Kafka, CI/CD, Git, Bitbucket</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec4f699ead9fde89</t>
+          <t>https://www.indeed.com/viewjob?jk=f4ac39415fc425cb</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Development Engineer 2</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Viventium Software</t>
+          <t>Twilio</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Dimensional Modeling, ETL, dbt, CI/CD, Airflow, Git</t>
+          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58073b2cbabb8cc1</t>
+          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Development Engineer 2</t>
+          <t>AI &amp; Data Scientist Intern</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Twilio</t>
+          <t>Ingredion</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Westchester, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Azure, GCP, Scala, Kafka, NoSQL, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee8fa84c7579b793</t>
+          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>AI &amp; Data Scientist Intern</t>
+          <t>Systems Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ingredion</t>
+          <t>First Onsite</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Westchester, IL, US USA</t>
+          <t>Greenwood Village, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Hadoop, Hive, Spark, Scala, NoSQL</t>
+          <t>AWS, Lambda, ECS, RDS, Azure, Scala, PostgreSQL, Terraform, AWS CloudFormation, Docker</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c1230ee3c5c180d</t>
+          <t>https://www.indeed.com/viewjob?jk=c875d0252524b8be</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
+          <t>Senior TDI Site Reliability Engineer, Okta Federal</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Texas Health and Human Services Commission</t>
+          <t>Okta</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
+          <t>AWS, IAM, RDS, Scala, Splunk, CI/CD, GitHub Actions, Terraform, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
+          <t>https://www.indeed.com/viewjob?jk=5dc7f3375ec1f830</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Entitlement I - Sr. Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>Burlington Stores</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Edgewater Park, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>Azure, Event Hubs, Spark, Spark Streaming, Kafka, Snowflake, Oracle, ETL, ELT, CI/CD</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45974b9c03dac7e0</t>
+          <t>https://www.indeed.com/viewjob?jk=f6d13e91fe3906c8</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Storage Platform Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>bluematrix</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,34 +3286,34 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Kinesis, SQS, ECS, Scala, PostgreSQL, CI/CD, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala, CI/CD</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6eff3f3607854e4a</t>
+          <t>https://www.indeed.com/viewjob?jk=32ec8aa7100f3fdb</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Sr Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Techtronic Industries Co. Ltd</t>
+          <t>Child Mind Institute</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Menomonee Falls, WI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,17 +3321,17 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
+          <t>AWS, RDS, Azure, Scala, Polars, NoSQL, ETL, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>2026-08-14</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
+          <t>https://www.indeed.com/viewjob?jk=2eed7b666dfdbc93</t>
         </is>
       </c>
     </row>
@@ -3373,17 +3373,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior Databricks Data Engineer - Reliability</t>
+          <t>Sr Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Scientific Games</t>
+          <t>Techtronic Industries Co. Ltd</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Menomonee Falls, WI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,34 +3391,34 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
+          <t>Kinesis, Databricks, Event Hubs, Unity Catalog, Delta Live Tables, Spark, Scala, Kafka, ELT, DataOps</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
+          <t>https://www.indeed.com/viewjob?jk=59b1255ab0bc1127</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Devops Engineer</t>
+          <t>Data Analyst IV - Advanced Analytics &amp; Reporting - 100% remote</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Texas Health and Human Services Commission</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,34 +3426,34 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
+          <t>RDS, Databricks, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
+          <t>https://www.indeed.com/viewjob?jk=4986a7e3a649da10</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Databricks Data Engineer - Reliability</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Truist</t>
+          <t>Scientific Games</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Databricks, Medallion Architecture, Spark, PySpark, Scala, Databricks Lakehouse, ETL, ELT</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
+          <t>https://www.indeed.com/viewjob?jk=d75159f3d153dc7a</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Full Stack Solutions Developer – Java</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Truist</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Data Modeling, Jenkins, Maven, Jenkins</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,7 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16d5fddfa3a804d4</t>
+          <t>https://www.indeed.com/viewjob?jk=9f81fcca5179d8dc</t>
         </is>
       </c>
     </row>
@@ -3548,17 +3548,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Sr. Database Developer</t>
+          <t>Devops Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Herschend Family Entertainment</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Peachtree Corners, GA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,34 +3566,34 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Databricks, Spark, Snowflake, Oracle, Cassandra, NoSQL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-09-02</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
+          <t>https://www.indeed.com/viewjob?jk=9bc2a89638158cad</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>APPLICATION DEVELOPER</t>
+          <t>Sr. Database Developer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Atos</t>
+          <t>Herschend Family Entertainment</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Aurora, IL, US USA</t>
+          <t>Peachtree Corners, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, MongoDB, NoSQL, CI/CD, Jenkins, Maven, Jenkins</t>
+          <t>AWS, RDS, Medallion Architecture, Spark, Scala, SQL Server, Dimensional Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,7 +3611,77 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88b7d6cdbfaa32a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e52ec8993f3a44ae</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>NoSQL Database Engineer || Onsite</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Ukund</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>San Francisco Bay Area, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, S3, IAM, GCP, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-02</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9314bc9cfb51fe1b</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Database Administrator (Remote)</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Neumo Holdings LLC</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, Data Modeling, CI/CD, Terraform</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e97f3541b9b4ed92</t>
         </is>
       </c>
     </row>
